--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:05:22+00:00</t>
+    <t>2024-04-25T09:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:06:15+00:00</t>
+    <t>2024-05-16T08:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-16T08:04:49+00:00</t>
+    <t>2024-05-23T12:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:00:22+00:00</t>
+    <t>2024-06-05T13:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:15:20+00:00</t>
+    <t>2024-06-05T13:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:17:40+00:00</t>
+    <t>2024-06-17T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
+++ b/main/ig/StructureDefinition-mesures-diabetis-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T15:07:22+00:00</t>
+    <t>2024-07-01T14:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
